--- a/backend/data/financials_by_company/1PGN.MI.xlsx
+++ b/backend/data/financials_by_company/1PGN.MI.xlsx
@@ -682,57 +682,59 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-959850</v>
+        <v>-303686.921372</v>
       </c>
       <c r="C2" t="n">
-        <v>0.15</v>
+        <v>0.06454600000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>24222000</v>
+        <v>19375000</v>
       </c>
       <c r="E2" t="n">
-        <v>-6399000</v>
+        <v>-4705000</v>
       </c>
       <c r="F2" t="n">
-        <v>-6399000</v>
+        <v>-4705000</v>
       </c>
       <c r="G2" t="n">
-        <v>-6105000</v>
+        <v>-7174000</v>
       </c>
       <c r="H2" t="n">
-        <v>17007000</v>
+        <v>16365000</v>
       </c>
       <c r="I2" t="n">
-        <v>67272000</v>
+        <v>67211000</v>
       </c>
       <c r="J2" t="n">
-        <v>17823000</v>
+        <v>14670000</v>
       </c>
       <c r="K2" t="n">
-        <v>816000</v>
+        <v>-1695000</v>
       </c>
       <c r="L2" t="n">
-        <v>-6488000</v>
+        <v>-5910000</v>
       </c>
       <c r="M2" t="n">
-        <v>6518000</v>
+        <v>5974000</v>
       </c>
       <c r="N2" t="n">
-        <v>30000</v>
+        <v>64000</v>
       </c>
       <c r="O2" t="n">
-        <v>-665850</v>
+        <v>-2772686.921372</v>
       </c>
       <c r="P2" t="n">
-        <v>-6105000</v>
+        <v>-11417000</v>
       </c>
       <c r="Q2" t="n">
-        <v>131368000</v>
-      </c>
-      <c r="R2" t="inlineStr"/>
+        <v>135226000</v>
+      </c>
+      <c r="R2" t="n">
+        <v>647000</v>
+      </c>
       <c r="S2" t="n">
         <v>4526266</v>
       </c>
@@ -740,149 +742,157 @@
         <v>4526266</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.35</v>
+        <v>-2.52</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.35</v>
+        <v>-2.52</v>
       </c>
       <c r="W2" t="n">
-        <v>-6105000</v>
+        <v>-11417000</v>
       </c>
       <c r="X2" t="n">
-        <v>-6105000</v>
+        <v>-11417000</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>-6105000</v>
+        <v>-11417000</v>
       </c>
       <c r="AA2" t="n">
-        <v>-6105000</v>
-      </c>
-      <c r="AB2" t="inlineStr"/>
+        <v>-11417000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>-4243000</v>
+      </c>
       <c r="AC2" t="n">
-        <v>-6105000</v>
+        <v>-7174000</v>
       </c>
       <c r="AD2" t="n">
-        <v>403000</v>
+        <v>-495000</v>
       </c>
       <c r="AE2" t="n">
-        <v>-5702000</v>
+        <v>-7669000</v>
       </c>
       <c r="AF2" t="n">
-        <v>-6399000</v>
+        <v>-4705000</v>
       </c>
       <c r="AG2" t="n">
-        <v>1653000</v>
+        <v>1672000</v>
       </c>
       <c r="AH2" t="n">
-        <v>98000</v>
+        <v>1013000</v>
       </c>
       <c r="AI2" t="n">
-        <v>4648000</v>
+        <v>2020000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-6488000</v>
-      </c>
-      <c r="AK2" t="inlineStr"/>
+        <v>-5910000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>3986000</v>
+      </c>
       <c r="AL2" t="n">
-        <v>6518000</v>
+        <v>5974000</v>
       </c>
       <c r="AM2" t="n">
-        <v>30000</v>
+        <v>64000</v>
       </c>
       <c r="AN2" t="n">
-        <v>7665000</v>
+        <v>4507000</v>
       </c>
       <c r="AO2" t="n">
-        <v>64096000</v>
+        <v>68015000</v>
       </c>
       <c r="AP2" t="n">
-        <v>7574000</v>
+        <v>8991000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>12359000</v>
+        <v>14346000</v>
       </c>
       <c r="AR2" t="n">
-        <v>12359000</v>
+        <v>14346000</v>
       </c>
       <c r="AS2" t="n">
-        <v>4891000</v>
+        <v>6990000</v>
       </c>
       <c r="AT2" t="n">
-        <v>1085000</v>
+        <v>479000</v>
       </c>
       <c r="AU2" t="n">
-        <v>3806000</v>
-      </c>
-      <c r="AV2" t="inlineStr"/>
+        <v>6511000</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>647000</v>
+      </c>
       <c r="AW2" t="n">
-        <v>71761000</v>
+        <v>72522000</v>
       </c>
       <c r="AX2" t="n">
-        <v>67272000</v>
+        <v>67211000</v>
       </c>
       <c r="AY2" t="n">
-        <v>139033000</v>
+        <v>139733000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>139033000</v>
+        <v>139733000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-400317.543401</v>
+        <v>-787391.180654</v>
       </c>
       <c r="C3" t="n">
-        <v>0.077641</v>
+        <v>0.204836</v>
       </c>
       <c r="D3" t="n">
-        <v>22779000</v>
+        <v>13757000</v>
       </c>
       <c r="E3" t="n">
-        <v>-5156000</v>
+        <v>-3844000</v>
       </c>
       <c r="F3" t="n">
-        <v>-5156000</v>
+        <v>-3844000</v>
       </c>
       <c r="G3" t="n">
-        <v>-10571000</v>
+        <v>-9503000</v>
       </c>
       <c r="H3" t="n">
-        <v>16432000</v>
+        <v>14278000</v>
       </c>
       <c r="I3" t="n">
-        <v>89138000</v>
+        <v>89408000</v>
       </c>
       <c r="J3" t="n">
-        <v>17623000</v>
+        <v>9913000</v>
       </c>
       <c r="K3" t="n">
-        <v>1191000</v>
+        <v>-4366000</v>
       </c>
       <c r="L3" t="n">
-        <v>-12512000</v>
+        <v>-7543000</v>
       </c>
       <c r="M3" t="n">
-        <v>12654000</v>
+        <v>7585000</v>
       </c>
       <c r="N3" t="n">
-        <v>142000</v>
+        <v>42000</v>
       </c>
       <c r="O3" t="n">
-        <v>-5815317.543401</v>
+        <v>-6446391.180654</v>
       </c>
       <c r="P3" t="n">
-        <v>-3812000</v>
+        <v>-4194000</v>
       </c>
       <c r="Q3" t="n">
-        <v>166865000</v>
-      </c>
-      <c r="R3" t="inlineStr"/>
+        <v>164243000</v>
+      </c>
+      <c r="R3" t="n">
+        <v>421000</v>
+      </c>
       <c r="S3" t="n">
         <v>4526266</v>
       </c>
@@ -890,153 +900,153 @@
         <v>4526266</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.84</v>
+        <v>-0.93</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.84</v>
+        <v>-0.93</v>
       </c>
       <c r="W3" t="n">
-        <v>-3812000</v>
+        <v>-4194000</v>
       </c>
       <c r="X3" t="n">
-        <v>-3812000</v>
+        <v>-4194000</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>-3812000</v>
+        <v>-4194000</v>
       </c>
       <c r="AA3" t="n">
-        <v>-3812000</v>
+        <v>-4194000</v>
       </c>
       <c r="AB3" t="n">
-        <v>6759000</v>
+        <v>5309000</v>
       </c>
       <c r="AC3" t="n">
-        <v>-10571000</v>
+        <v>-9503000</v>
       </c>
       <c r="AD3" t="n">
-        <v>-890000</v>
+        <v>-2448000</v>
       </c>
       <c r="AE3" t="n">
-        <v>-11463000</v>
+        <v>-11951000</v>
       </c>
       <c r="AF3" t="n">
-        <v>-5156000</v>
+        <v>-3844000</v>
       </c>
       <c r="AG3" t="n">
-        <v>4135000</v>
+        <v>3080000</v>
       </c>
       <c r="AH3" t="n">
-        <v>834000</v>
+        <v>446000</v>
       </c>
       <c r="AI3" t="n">
-        <v>187000</v>
+        <v>318000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-12512000</v>
+        <v>-7543000</v>
       </c>
       <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="n">
-        <v>12654000</v>
+        <v>7585000</v>
       </c>
       <c r="AM3" t="n">
-        <v>142000</v>
+        <v>42000</v>
       </c>
       <c r="AN3" t="n">
-        <v>6846000</v>
+        <v>1076000</v>
       </c>
       <c r="AO3" t="n">
-        <v>77727000</v>
+        <v>74835000</v>
       </c>
       <c r="AP3" t="n">
-        <v>11414000</v>
+        <v>11453000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>16432000</v>
+        <v>14279000</v>
       </c>
       <c r="AR3" t="n">
-        <v>16432000</v>
+        <v>14279000</v>
       </c>
       <c r="AS3" t="n">
-        <v>5435000</v>
+        <v>7833000</v>
       </c>
       <c r="AT3" t="n">
-        <v>1206000</v>
+        <v>1817000</v>
       </c>
       <c r="AU3" t="n">
-        <v>4229000</v>
-      </c>
-      <c r="AV3" t="inlineStr"/>
+        <v>6016000</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>421000</v>
+      </c>
       <c r="AW3" t="n">
-        <v>84573000</v>
+        <v>75911000</v>
       </c>
       <c r="AX3" t="n">
-        <v>89138000</v>
+        <v>89408000</v>
       </c>
       <c r="AY3" t="n">
-        <v>173711000</v>
+        <v>165319000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>173711000</v>
+        <v>165319000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-787391.180654</v>
+        <v>-400317.543401</v>
       </c>
       <c r="C4" t="n">
-        <v>0.204836</v>
+        <v>0.077641</v>
       </c>
       <c r="D4" t="n">
-        <v>13757000</v>
+        <v>22779000</v>
       </c>
       <c r="E4" t="n">
-        <v>-3844000</v>
+        <v>-5156000</v>
       </c>
       <c r="F4" t="n">
-        <v>-3844000</v>
+        <v>-5156000</v>
       </c>
       <c r="G4" t="n">
-        <v>-9503000</v>
+        <v>-10571000</v>
       </c>
       <c r="H4" t="n">
-        <v>14278000</v>
+        <v>16432000</v>
       </c>
       <c r="I4" t="n">
-        <v>89408000</v>
+        <v>89138000</v>
       </c>
       <c r="J4" t="n">
-        <v>9913000</v>
+        <v>17623000</v>
       </c>
       <c r="K4" t="n">
-        <v>-4366000</v>
+        <v>1191000</v>
       </c>
       <c r="L4" t="n">
-        <v>-7543000</v>
+        <v>-12512000</v>
       </c>
       <c r="M4" t="n">
-        <v>7585000</v>
+        <v>12654000</v>
       </c>
       <c r="N4" t="n">
-        <v>42000</v>
+        <v>142000</v>
       </c>
       <c r="O4" t="n">
-        <v>-6446391.180654</v>
+        <v>-5815317.543401</v>
       </c>
       <c r="P4" t="n">
-        <v>-4194000</v>
+        <v>-3812000</v>
       </c>
       <c r="Q4" t="n">
-        <v>164243000</v>
-      </c>
-      <c r="R4" t="n">
-        <v>421000</v>
-      </c>
+        <v>166865000</v>
+      </c>
+      <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
         <v>4526266</v>
       </c>
@@ -1044,155 +1054,151 @@
         <v>4526266</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.93</v>
+        <v>-0.84</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.93</v>
+        <v>-0.84</v>
       </c>
       <c r="W4" t="n">
-        <v>-4194000</v>
+        <v>-3812000</v>
       </c>
       <c r="X4" t="n">
-        <v>-4194000</v>
+        <v>-3812000</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>-4194000</v>
+        <v>-3812000</v>
       </c>
       <c r="AA4" t="n">
-        <v>-4194000</v>
+        <v>-3812000</v>
       </c>
       <c r="AB4" t="n">
-        <v>5309000</v>
+        <v>6759000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-9503000</v>
+        <v>-10571000</v>
       </c>
       <c r="AD4" t="n">
-        <v>-2448000</v>
+        <v>-890000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-11951000</v>
+        <v>-11463000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-3844000</v>
+        <v>-5156000</v>
       </c>
       <c r="AG4" t="n">
-        <v>3080000</v>
+        <v>4135000</v>
       </c>
       <c r="AH4" t="n">
-        <v>446000</v>
+        <v>834000</v>
       </c>
       <c r="AI4" t="n">
-        <v>318000</v>
+        <v>187000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-7543000</v>
+        <v>-12512000</v>
       </c>
       <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="n">
-        <v>7585000</v>
+        <v>12654000</v>
       </c>
       <c r="AM4" t="n">
-        <v>42000</v>
+        <v>142000</v>
       </c>
       <c r="AN4" t="n">
-        <v>1076000</v>
+        <v>6846000</v>
       </c>
       <c r="AO4" t="n">
-        <v>74835000</v>
+        <v>77727000</v>
       </c>
       <c r="AP4" t="n">
-        <v>11453000</v>
+        <v>11414000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>14279000</v>
+        <v>16432000</v>
       </c>
       <c r="AR4" t="n">
-        <v>14279000</v>
+        <v>16432000</v>
       </c>
       <c r="AS4" t="n">
-        <v>7833000</v>
+        <v>5435000</v>
       </c>
       <c r="AT4" t="n">
-        <v>1817000</v>
+        <v>1206000</v>
       </c>
       <c r="AU4" t="n">
-        <v>6016000</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>421000</v>
-      </c>
+        <v>4229000</v>
+      </c>
+      <c r="AV4" t="inlineStr"/>
       <c r="AW4" t="n">
-        <v>75911000</v>
+        <v>84573000</v>
       </c>
       <c r="AX4" t="n">
-        <v>89408000</v>
+        <v>89138000</v>
       </c>
       <c r="AY4" t="n">
-        <v>165319000</v>
+        <v>173711000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>165319000</v>
+        <v>173711000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-303686.921372</v>
+        <v>-959850</v>
       </c>
       <c r="C5" t="n">
-        <v>0.06454600000000001</v>
+        <v>0.15</v>
       </c>
       <c r="D5" t="n">
-        <v>19375000</v>
+        <v>24222000</v>
       </c>
       <c r="E5" t="n">
-        <v>-4705000</v>
+        <v>-6399000</v>
       </c>
       <c r="F5" t="n">
-        <v>-4705000</v>
+        <v>-6399000</v>
       </c>
       <c r="G5" t="n">
-        <v>-7174000</v>
+        <v>-6105000</v>
       </c>
       <c r="H5" t="n">
-        <v>16365000</v>
+        <v>17007000</v>
       </c>
       <c r="I5" t="n">
-        <v>67211000</v>
+        <v>67272000</v>
       </c>
       <c r="J5" t="n">
-        <v>14670000</v>
+        <v>17823000</v>
       </c>
       <c r="K5" t="n">
-        <v>-1695000</v>
+        <v>816000</v>
       </c>
       <c r="L5" t="n">
-        <v>-5910000</v>
+        <v>-6488000</v>
       </c>
       <c r="M5" t="n">
-        <v>5974000</v>
+        <v>6518000</v>
       </c>
       <c r="N5" t="n">
-        <v>64000</v>
+        <v>30000</v>
       </c>
       <c r="O5" t="n">
-        <v>-2772686.921372</v>
+        <v>-665850</v>
       </c>
       <c r="P5" t="n">
-        <v>-11417000</v>
+        <v>-6105000</v>
       </c>
       <c r="Q5" t="n">
-        <v>135226000</v>
-      </c>
-      <c r="R5" t="n">
-        <v>647000</v>
-      </c>
+        <v>131368000</v>
+      </c>
+      <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
         <v>4526266</v>
       </c>
@@ -1200,100 +1206,94 @@
         <v>4526266</v>
       </c>
       <c r="U5" t="n">
-        <v>-2.52</v>
+        <v>-1.35</v>
       </c>
       <c r="V5" t="n">
-        <v>-2.52</v>
+        <v>-1.35</v>
       </c>
       <c r="W5" t="n">
-        <v>-11417000</v>
+        <v>-6105000</v>
       </c>
       <c r="X5" t="n">
-        <v>-11417000</v>
+        <v>-6105000</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>-11417000</v>
+        <v>-6105000</v>
       </c>
       <c r="AA5" t="n">
-        <v>-11417000</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>-4243000</v>
-      </c>
+        <v>-6105000</v>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="n">
-        <v>-7174000</v>
+        <v>-6105000</v>
       </c>
       <c r="AD5" t="n">
-        <v>-495000</v>
+        <v>403000</v>
       </c>
       <c r="AE5" t="n">
-        <v>-7669000</v>
+        <v>-5702000</v>
       </c>
       <c r="AF5" t="n">
-        <v>-4705000</v>
+        <v>-6399000</v>
       </c>
       <c r="AG5" t="n">
-        <v>1672000</v>
+        <v>1653000</v>
       </c>
       <c r="AH5" t="n">
-        <v>1013000</v>
+        <v>98000</v>
       </c>
       <c r="AI5" t="n">
-        <v>2020000</v>
+        <v>4648000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-5910000</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>3986000</v>
-      </c>
+        <v>-6488000</v>
+      </c>
+      <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="n">
-        <v>5974000</v>
+        <v>6518000</v>
       </c>
       <c r="AM5" t="n">
-        <v>64000</v>
+        <v>30000</v>
       </c>
       <c r="AN5" t="n">
-        <v>4507000</v>
+        <v>7665000</v>
       </c>
       <c r="AO5" t="n">
-        <v>68015000</v>
+        <v>64096000</v>
       </c>
       <c r="AP5" t="n">
-        <v>8991000</v>
+        <v>7574000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>14346000</v>
+        <v>12359000</v>
       </c>
       <c r="AR5" t="n">
-        <v>14346000</v>
+        <v>12359000</v>
       </c>
       <c r="AS5" t="n">
-        <v>6990000</v>
+        <v>4891000</v>
       </c>
       <c r="AT5" t="n">
-        <v>479000</v>
+        <v>1085000</v>
       </c>
       <c r="AU5" t="n">
-        <v>6511000</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>647000</v>
-      </c>
+        <v>3806000</v>
+      </c>
+      <c r="AV5" t="inlineStr"/>
       <c r="AW5" t="n">
-        <v>72522000</v>
+        <v>71761000</v>
       </c>
       <c r="AX5" t="n">
-        <v>67211000</v>
+        <v>67272000</v>
       </c>
       <c r="AY5" t="n">
-        <v>139733000</v>
+        <v>139033000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>139733000</v>
+        <v>139033000</v>
       </c>
     </row>
   </sheetData>
@@ -1704,7 +1704,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
         <v>4526266</v>
@@ -1713,44 +1713,46 @@
         <v>4526266</v>
       </c>
       <c r="D2" t="n">
-        <v>54827000</v>
+        <v>102345000</v>
       </c>
       <c r="E2" t="n">
-        <v>69352000</v>
+        <v>115878000</v>
       </c>
       <c r="F2" t="n">
-        <v>-45601000</v>
+        <v>-73106000</v>
       </c>
       <c r="G2" t="n">
-        <v>49265000</v>
+        <v>107101000</v>
       </c>
       <c r="H2" t="n">
-        <v>-31917000</v>
+        <v>-83852000</v>
       </c>
       <c r="I2" t="n">
-        <v>-45601000</v>
+        <v>-73106000</v>
       </c>
       <c r="J2" t="n">
-        <v>10134000</v>
+        <v>12078000</v>
       </c>
       <c r="K2" t="n">
-        <v>-9953000</v>
+        <v>3301000</v>
       </c>
       <c r="L2" t="n">
-        <v>20649000</v>
+        <v>13483000</v>
       </c>
       <c r="M2" t="n">
-        <v>-9953000</v>
-      </c>
-      <c r="N2" t="inlineStr"/>
+        <v>3301000</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
       <c r="O2" t="n">
-        <v>-9953000</v>
+        <v>3301000</v>
       </c>
       <c r="P2" t="n">
-        <v>175000</v>
+        <v>-677000</v>
       </c>
       <c r="Q2" t="n">
-        <v>-30395000</v>
+        <v>-16283000</v>
       </c>
       <c r="R2" t="n">
         <v>15485000</v>
@@ -1762,166 +1764,178 @@
         <v>4526000</v>
       </c>
       <c r="U2" t="n">
-        <v>108270000</v>
+        <v>156368000</v>
       </c>
       <c r="V2" t="n">
-        <v>41104000</v>
-      </c>
-      <c r="W2" t="inlineStr"/>
+        <v>28300000</v>
+      </c>
+      <c r="W2" t="n">
+        <v>-1000</v>
+      </c>
       <c r="X2" t="n">
-        <v>1924000</v>
+        <v>2931000</v>
       </c>
       <c r="Y2" t="n">
-        <v>61000</v>
+        <v>5692000</v>
       </c>
       <c r="Z2" t="n">
-        <v>37994000</v>
+        <v>19678000</v>
       </c>
       <c r="AA2" t="n">
-        <v>7392000</v>
+        <v>9496000</v>
       </c>
       <c r="AB2" t="n">
-        <v>30602000</v>
+        <v>10182000</v>
       </c>
       <c r="AC2" t="n">
-        <v>67166000</v>
+        <v>128068000</v>
       </c>
       <c r="AD2" t="n">
-        <v>2310000</v>
+        <v>862000</v>
       </c>
       <c r="AE2" t="n">
-        <v>31358000</v>
+        <v>96200000</v>
       </c>
       <c r="AF2" t="n">
-        <v>2742000</v>
+        <v>2582000</v>
       </c>
       <c r="AG2" t="n">
-        <v>28616000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>5027000</v>
-      </c>
-      <c r="AI2" t="inlineStr"/>
+        <v>93618000</v>
+      </c>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="n">
+        <v>2015000</v>
+      </c>
       <c r="AJ2" t="n">
-        <v>26077000</v>
-      </c>
-      <c r="AK2" t="inlineStr"/>
+        <v>28986000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>6178000</v>
+      </c>
       <c r="AL2" t="n">
-        <v>1483000</v>
+        <v>8938000</v>
       </c>
       <c r="AM2" t="n">
-        <v>24594000</v>
+        <v>13870000</v>
       </c>
       <c r="AN2" t="n">
-        <v>98317000</v>
+        <v>159669000</v>
       </c>
       <c r="AO2" t="n">
-        <v>63069000</v>
+        <v>115453000</v>
       </c>
       <c r="AP2" t="n">
-        <v>419000</v>
-      </c>
-      <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="inlineStr"/>
+        <v>475000</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>574000</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>574000</v>
+      </c>
       <c r="AT2" t="n">
-        <v>1642000</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>1642000</v>
-      </c>
+        <v>574000</v>
+      </c>
+      <c r="AU2" t="inlineStr"/>
       <c r="AV2" t="inlineStr"/>
       <c r="AW2" t="n">
-        <v>35648000</v>
+        <v>76407000</v>
       </c>
       <c r="AX2" t="n">
-        <v>29903000</v>
+        <v>54532000</v>
       </c>
       <c r="AY2" t="n">
-        <v>5745000</v>
+        <v>21875000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>25360000</v>
+        <v>37997000</v>
       </c>
       <c r="BA2" t="n">
-        <v>-27251000</v>
+        <v>-22654000</v>
       </c>
       <c r="BB2" t="n">
-        <v>52611000</v>
+        <v>60651000</v>
       </c>
       <c r="BC2" t="n">
-        <v>2421000</v>
+        <v>2416000</v>
       </c>
       <c r="BD2" t="n">
-        <v>5641000</v>
+        <v>4227000</v>
       </c>
       <c r="BE2" t="n">
-        <v>19366000</v>
+        <v>25408000</v>
       </c>
       <c r="BF2" t="n">
-        <v>10511000</v>
+        <v>2780000</v>
       </c>
       <c r="BG2" t="n">
-        <v>14672000</v>
+        <v>25820000</v>
       </c>
       <c r="BH2" t="n">
         <v>0</v>
       </c>
       <c r="BI2" t="n">
-        <v>35249000</v>
+        <v>44216000</v>
       </c>
       <c r="BJ2" t="n">
-        <v>2689000</v>
-      </c>
-      <c r="BK2" t="inlineStr"/>
+        <v>7716000</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>1004000</v>
+      </c>
       <c r="BL2" t="n">
-        <v>281000</v>
-      </c>
-      <c r="BM2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>169000</v>
+      </c>
       <c r="BN2" t="n">
-        <v>646000</v>
+        <v>776000</v>
       </c>
       <c r="BO2" t="n">
-        <v>15908000</v>
+        <v>23189000</v>
       </c>
       <c r="BP2" t="n">
-        <v>2572000</v>
+        <v>6357000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>13336000</v>
+        <v>16832000</v>
       </c>
       <c r="BR2" t="n">
-        <v>4923000</v>
+        <v>3252000</v>
       </c>
       <c r="BS2" t="n">
-        <v>19000</v>
+        <v>221000</v>
       </c>
       <c r="BT2" t="n">
-        <v>5398000</v>
+        <v>10859000</v>
       </c>
       <c r="BU2" t="n">
-        <v>-500000</v>
+        <v>-2813000</v>
       </c>
       <c r="BV2" t="n">
-        <v>5898000</v>
+        <v>13672000</v>
       </c>
       <c r="BW2" t="n">
-        <v>5385000</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>994000</v>
-      </c>
+        <v>1455000</v>
+      </c>
+      <c r="BX2" t="inlineStr"/>
       <c r="BY2" t="n">
-        <v>4391000</v>
-      </c>
-      <c r="BZ2" t="inlineStr"/>
+        <v>1455000</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>1446000</v>
+      </c>
       <c r="CA2" t="n">
-        <v>4391000</v>
+        <v>1455000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
         <v>4526266</v>
@@ -1930,44 +1944,44 @@
         <v>4526266</v>
       </c>
       <c r="D3" t="n">
-        <v>57651000</v>
+        <v>87323000</v>
       </c>
       <c r="E3" t="n">
-        <v>72505000</v>
+        <v>119518000</v>
       </c>
       <c r="F3" t="n">
-        <v>-43540000</v>
+        <v>-43270000</v>
       </c>
       <c r="G3" t="n">
-        <v>56777000</v>
+        <v>105264000</v>
       </c>
       <c r="H3" t="n">
-        <v>-28428000</v>
+        <v>-9220000</v>
       </c>
       <c r="I3" t="n">
-        <v>-43540000</v>
+        <v>-43270000</v>
       </c>
       <c r="J3" t="n">
-        <v>11645000</v>
+        <v>14089000</v>
       </c>
       <c r="K3" t="n">
-        <v>-4083000</v>
+        <v>-165000</v>
       </c>
       <c r="L3" t="n">
-        <v>26743000</v>
+        <v>52148000</v>
       </c>
       <c r="M3" t="n">
-        <v>-4083000</v>
+        <v>-165000</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
-        <v>-4083000</v>
+        <v>-165000</v>
       </c>
       <c r="P3" t="n">
-        <v>64000</v>
+        <v>21000</v>
       </c>
       <c r="Q3" t="n">
-        <v>-24290000</v>
+        <v>-20478000</v>
       </c>
       <c r="R3" t="n">
         <v>15485000</v>
@@ -1979,174 +1993,180 @@
         <v>4526000</v>
       </c>
       <c r="U3" t="n">
-        <v>112603000</v>
+        <v>172777000</v>
       </c>
       <c r="V3" t="n">
-        <v>43930000</v>
+        <v>66991000</v>
       </c>
       <c r="W3" t="n">
         <v>-1000</v>
       </c>
       <c r="X3" t="n">
-        <v>1921000</v>
+        <v>2383000</v>
       </c>
       <c r="Y3" t="n">
-        <v>292000</v>
+        <v>1211000</v>
       </c>
       <c r="Z3" t="n">
-        <v>39513000</v>
+        <v>62023000</v>
       </c>
       <c r="AA3" t="n">
-        <v>8687000</v>
+        <v>9710000</v>
       </c>
       <c r="AB3" t="n">
-        <v>30826000</v>
+        <v>52313000</v>
       </c>
       <c r="AC3" t="n">
-        <v>68673000</v>
+        <v>105786000</v>
       </c>
       <c r="AD3" t="n">
-        <v>2159000</v>
+        <v>1352000</v>
       </c>
       <c r="AE3" t="n">
-        <v>32992000</v>
+        <v>57495000</v>
       </c>
       <c r="AF3" t="n">
-        <v>2958000</v>
+        <v>4379000</v>
       </c>
       <c r="AG3" t="n">
-        <v>30034000</v>
+        <v>53116000</v>
       </c>
       <c r="AH3" t="n">
-        <v>5032000</v>
+        <v>3298000</v>
       </c>
       <c r="AI3" t="n">
-        <v>488000</v>
+        <v>273000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>25370000</v>
-      </c>
-      <c r="AK3" t="inlineStr"/>
+        <v>36513000</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>4978000</v>
+      </c>
       <c r="AL3" t="n">
-        <v>996000</v>
+        <v>11563000</v>
       </c>
       <c r="AM3" t="n">
-        <v>24374000</v>
+        <v>24950000</v>
       </c>
       <c r="AN3" t="n">
-        <v>108520000</v>
+        <v>172612000</v>
       </c>
       <c r="AO3" t="n">
-        <v>68274000</v>
+        <v>76046000</v>
       </c>
       <c r="AP3" t="n">
-        <v>456000</v>
+        <v>471000</v>
       </c>
       <c r="AQ3" t="inlineStr"/>
       <c r="AR3" t="inlineStr"/>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
-        <v>1642000</v>
+        <v>1643000</v>
       </c>
       <c r="AU3" t="n">
-        <v>1642000</v>
+        <v>1643000</v>
       </c>
       <c r="AV3" t="n">
-        <v>120000</v>
+        <v>121000</v>
       </c>
       <c r="AW3" t="n">
-        <v>39457000</v>
+        <v>43105000</v>
       </c>
       <c r="AX3" t="n">
-        <v>33712000</v>
+        <v>37360000</v>
       </c>
       <c r="AY3" t="n">
         <v>5745000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>26719000</v>
+        <v>30827000</v>
       </c>
       <c r="BA3" t="n">
-        <v>-27148000</v>
+        <v>-23681000</v>
       </c>
       <c r="BB3" t="n">
-        <v>53867000</v>
+        <v>54508000</v>
       </c>
       <c r="BC3" t="n">
-        <v>3306000</v>
+        <v>2596000</v>
       </c>
       <c r="BD3" t="n">
-        <v>8924000</v>
+        <v>9497000</v>
       </c>
       <c r="BE3" t="n">
-        <v>18077000</v>
+        <v>18936000</v>
       </c>
       <c r="BF3" t="n">
-        <v>9599000</v>
+        <v>9554000</v>
       </c>
       <c r="BG3" t="n">
-        <v>13961000</v>
+        <v>13925000</v>
       </c>
       <c r="BH3" t="n">
         <v>0</v>
       </c>
       <c r="BI3" t="n">
-        <v>40245000</v>
+        <v>96566000</v>
       </c>
       <c r="BJ3" t="n">
-        <v>3095000</v>
+        <v>4363000</v>
       </c>
       <c r="BK3" t="n">
         <v>0</v>
       </c>
       <c r="BL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM3" t="inlineStr"/>
+        <v>35771000</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>424000</v>
+      </c>
       <c r="BN3" t="n">
-        <v>128000</v>
+        <v>836000</v>
       </c>
       <c r="BO3" t="n">
-        <v>20513000</v>
+        <v>23173000</v>
       </c>
       <c r="BP3" t="n">
-        <v>4510000</v>
+        <v>5540000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>16003000</v>
+        <v>17633000</v>
       </c>
       <c r="BR3" t="n">
-        <v>4129000</v>
+        <v>4433000</v>
       </c>
       <c r="BS3" t="n">
-        <v>0</v>
+        <v>217000</v>
       </c>
       <c r="BT3" t="n">
-        <v>6646000</v>
+        <v>7660000</v>
       </c>
       <c r="BU3" t="n">
-        <v>-1190000</v>
+        <v>-2620000</v>
       </c>
       <c r="BV3" t="n">
-        <v>7836000</v>
+        <v>10280000</v>
       </c>
       <c r="BW3" t="n">
-        <v>5734000</v>
+        <v>20113000</v>
       </c>
       <c r="BX3" t="n">
-        <v>2525000</v>
+        <v>2007000</v>
       </c>
       <c r="BY3" t="n">
-        <v>3209000</v>
-      </c>
-      <c r="BZ3" t="inlineStr"/>
+        <v>18106000</v>
+      </c>
+      <c r="BZ3" t="n">
+        <v>18098000</v>
+      </c>
       <c r="CA3" t="n">
-        <v>3209000</v>
+        <v>18106000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
         <v>4526266</v>
@@ -2155,44 +2175,44 @@
         <v>4526266</v>
       </c>
       <c r="D4" t="n">
-        <v>87323000</v>
+        <v>57651000</v>
       </c>
       <c r="E4" t="n">
-        <v>119518000</v>
+        <v>72505000</v>
       </c>
       <c r="F4" t="n">
-        <v>-43270000</v>
+        <v>-43540000</v>
       </c>
       <c r="G4" t="n">
-        <v>105264000</v>
+        <v>56777000</v>
       </c>
       <c r="H4" t="n">
-        <v>-9220000</v>
+        <v>-28428000</v>
       </c>
       <c r="I4" t="n">
-        <v>-43270000</v>
+        <v>-43540000</v>
       </c>
       <c r="J4" t="n">
-        <v>14089000</v>
+        <v>11645000</v>
       </c>
       <c r="K4" t="n">
-        <v>-165000</v>
+        <v>-4083000</v>
       </c>
       <c r="L4" t="n">
-        <v>52148000</v>
+        <v>26743000</v>
       </c>
       <c r="M4" t="n">
-        <v>-165000</v>
+        <v>-4083000</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
-        <v>-165000</v>
+        <v>-4083000</v>
       </c>
       <c r="P4" t="n">
-        <v>21000</v>
+        <v>64000</v>
       </c>
       <c r="Q4" t="n">
-        <v>-20478000</v>
+        <v>-24290000</v>
       </c>
       <c r="R4" t="n">
         <v>15485000</v>
@@ -2204,180 +2224,174 @@
         <v>4526000</v>
       </c>
       <c r="U4" t="n">
-        <v>172777000</v>
+        <v>112603000</v>
       </c>
       <c r="V4" t="n">
-        <v>66991000</v>
+        <v>43930000</v>
       </c>
       <c r="W4" t="n">
         <v>-1000</v>
       </c>
       <c r="X4" t="n">
-        <v>2383000</v>
+        <v>1921000</v>
       </c>
       <c r="Y4" t="n">
-        <v>1211000</v>
+        <v>292000</v>
       </c>
       <c r="Z4" t="n">
-        <v>62023000</v>
+        <v>39513000</v>
       </c>
       <c r="AA4" t="n">
-        <v>9710000</v>
+        <v>8687000</v>
       </c>
       <c r="AB4" t="n">
-        <v>52313000</v>
+        <v>30826000</v>
       </c>
       <c r="AC4" t="n">
-        <v>105786000</v>
+        <v>68673000</v>
       </c>
       <c r="AD4" t="n">
-        <v>1352000</v>
+        <v>2159000</v>
       </c>
       <c r="AE4" t="n">
-        <v>57495000</v>
+        <v>32992000</v>
       </c>
       <c r="AF4" t="n">
-        <v>4379000</v>
+        <v>2958000</v>
       </c>
       <c r="AG4" t="n">
-        <v>53116000</v>
+        <v>30034000</v>
       </c>
       <c r="AH4" t="n">
-        <v>3298000</v>
+        <v>5032000</v>
       </c>
       <c r="AI4" t="n">
-        <v>273000</v>
+        <v>488000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>36513000</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>4978000</v>
-      </c>
+        <v>25370000</v>
+      </c>
+      <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="n">
-        <v>11563000</v>
+        <v>996000</v>
       </c>
       <c r="AM4" t="n">
-        <v>24950000</v>
+        <v>24374000</v>
       </c>
       <c r="AN4" t="n">
-        <v>172612000</v>
+        <v>108520000</v>
       </c>
       <c r="AO4" t="n">
-        <v>76046000</v>
+        <v>68274000</v>
       </c>
       <c r="AP4" t="n">
-        <v>471000</v>
+        <v>456000</v>
       </c>
       <c r="AQ4" t="inlineStr"/>
       <c r="AR4" t="inlineStr"/>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
-        <v>1643000</v>
+        <v>1642000</v>
       </c>
       <c r="AU4" t="n">
-        <v>1643000</v>
+        <v>1642000</v>
       </c>
       <c r="AV4" t="n">
-        <v>121000</v>
+        <v>120000</v>
       </c>
       <c r="AW4" t="n">
-        <v>43105000</v>
+        <v>39457000</v>
       </c>
       <c r="AX4" t="n">
-        <v>37360000</v>
+        <v>33712000</v>
       </c>
       <c r="AY4" t="n">
         <v>5745000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>30827000</v>
+        <v>26719000</v>
       </c>
       <c r="BA4" t="n">
-        <v>-23681000</v>
+        <v>-27148000</v>
       </c>
       <c r="BB4" t="n">
-        <v>54508000</v>
+        <v>53867000</v>
       </c>
       <c r="BC4" t="n">
-        <v>2596000</v>
+        <v>3306000</v>
       </c>
       <c r="BD4" t="n">
-        <v>9497000</v>
+        <v>8924000</v>
       </c>
       <c r="BE4" t="n">
-        <v>18936000</v>
+        <v>18077000</v>
       </c>
       <c r="BF4" t="n">
-        <v>9554000</v>
+        <v>9599000</v>
       </c>
       <c r="BG4" t="n">
-        <v>13925000</v>
+        <v>13961000</v>
       </c>
       <c r="BH4" t="n">
         <v>0</v>
       </c>
       <c r="BI4" t="n">
-        <v>96566000</v>
+        <v>40245000</v>
       </c>
       <c r="BJ4" t="n">
-        <v>4363000</v>
+        <v>3095000</v>
       </c>
       <c r="BK4" t="n">
         <v>0</v>
       </c>
       <c r="BL4" t="n">
-        <v>35771000</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>424000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="BM4" t="inlineStr"/>
       <c r="BN4" t="n">
-        <v>836000</v>
+        <v>128000</v>
       </c>
       <c r="BO4" t="n">
-        <v>23173000</v>
+        <v>20513000</v>
       </c>
       <c r="BP4" t="n">
-        <v>5540000</v>
+        <v>4510000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>17633000</v>
+        <v>16003000</v>
       </c>
       <c r="BR4" t="n">
-        <v>4433000</v>
+        <v>4129000</v>
       </c>
       <c r="BS4" t="n">
-        <v>217000</v>
+        <v>0</v>
       </c>
       <c r="BT4" t="n">
-        <v>7660000</v>
+        <v>6646000</v>
       </c>
       <c r="BU4" t="n">
-        <v>-2620000</v>
+        <v>-1190000</v>
       </c>
       <c r="BV4" t="n">
-        <v>10280000</v>
+        <v>7836000</v>
       </c>
       <c r="BW4" t="n">
-        <v>20113000</v>
+        <v>5734000</v>
       </c>
       <c r="BX4" t="n">
-        <v>2007000</v>
+        <v>2525000</v>
       </c>
       <c r="BY4" t="n">
-        <v>18106000</v>
-      </c>
-      <c r="BZ4" t="n">
-        <v>18098000</v>
-      </c>
+        <v>3209000</v>
+      </c>
+      <c r="BZ4" t="inlineStr"/>
       <c r="CA4" t="n">
-        <v>18106000</v>
+        <v>3209000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
         <v>4526266</v>
@@ -2386,46 +2400,44 @@
         <v>4526266</v>
       </c>
       <c r="D5" t="n">
-        <v>102345000</v>
+        <v>54827000</v>
       </c>
       <c r="E5" t="n">
-        <v>115878000</v>
+        <v>69352000</v>
       </c>
       <c r="F5" t="n">
-        <v>-73106000</v>
+        <v>-45601000</v>
       </c>
       <c r="G5" t="n">
-        <v>107101000</v>
+        <v>49265000</v>
       </c>
       <c r="H5" t="n">
-        <v>-83852000</v>
+        <v>-31917000</v>
       </c>
       <c r="I5" t="n">
-        <v>-73106000</v>
+        <v>-45601000</v>
       </c>
       <c r="J5" t="n">
-        <v>12078000</v>
+        <v>10134000</v>
       </c>
       <c r="K5" t="n">
-        <v>3301000</v>
+        <v>-9953000</v>
       </c>
       <c r="L5" t="n">
-        <v>13483000</v>
+        <v>20649000</v>
       </c>
       <c r="M5" t="n">
-        <v>3301000</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
+        <v>-9953000</v>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
-        <v>3301000</v>
+        <v>-9953000</v>
       </c>
       <c r="P5" t="n">
-        <v>-677000</v>
+        <v>175000</v>
       </c>
       <c r="Q5" t="n">
-        <v>-16283000</v>
+        <v>-30395000</v>
       </c>
       <c r="R5" t="n">
         <v>15485000</v>
@@ -2437,173 +2449,161 @@
         <v>4526000</v>
       </c>
       <c r="U5" t="n">
-        <v>156368000</v>
+        <v>108270000</v>
       </c>
       <c r="V5" t="n">
-        <v>28300000</v>
-      </c>
-      <c r="W5" t="n">
-        <v>-1000</v>
-      </c>
+        <v>41104000</v>
+      </c>
+      <c r="W5" t="inlineStr"/>
       <c r="X5" t="n">
-        <v>2931000</v>
+        <v>1924000</v>
       </c>
       <c r="Y5" t="n">
-        <v>5692000</v>
+        <v>61000</v>
       </c>
       <c r="Z5" t="n">
-        <v>19678000</v>
+        <v>37994000</v>
       </c>
       <c r="AA5" t="n">
-        <v>9496000</v>
+        <v>7392000</v>
       </c>
       <c r="AB5" t="n">
-        <v>10182000</v>
+        <v>30602000</v>
       </c>
       <c r="AC5" t="n">
-        <v>128068000</v>
+        <v>67166000</v>
       </c>
       <c r="AD5" t="n">
-        <v>862000</v>
+        <v>2310000</v>
       </c>
       <c r="AE5" t="n">
-        <v>96200000</v>
+        <v>31358000</v>
       </c>
       <c r="AF5" t="n">
-        <v>2582000</v>
+        <v>2742000</v>
       </c>
       <c r="AG5" t="n">
-        <v>93618000</v>
-      </c>
-      <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="n">
-        <v>2015000</v>
-      </c>
+        <v>28616000</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>5027000</v>
+      </c>
+      <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="n">
-        <v>28986000</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>6178000</v>
-      </c>
+        <v>26077000</v>
+      </c>
+      <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="n">
-        <v>8938000</v>
+        <v>1483000</v>
       </c>
       <c r="AM5" t="n">
-        <v>13870000</v>
+        <v>24594000</v>
       </c>
       <c r="AN5" t="n">
-        <v>159669000</v>
+        <v>98317000</v>
       </c>
       <c r="AO5" t="n">
-        <v>115453000</v>
+        <v>63069000</v>
       </c>
       <c r="AP5" t="n">
-        <v>475000</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>574000</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>574000</v>
-      </c>
+        <v>419000</v>
+      </c>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
-        <v>574000</v>
-      </c>
-      <c r="AU5" t="inlineStr"/>
+        <v>1642000</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>1642000</v>
+      </c>
       <c r="AV5" t="inlineStr"/>
       <c r="AW5" t="n">
-        <v>76407000</v>
+        <v>35648000</v>
       </c>
       <c r="AX5" t="n">
-        <v>54532000</v>
+        <v>29903000</v>
       </c>
       <c r="AY5" t="n">
-        <v>21875000</v>
+        <v>5745000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>37997000</v>
+        <v>25360000</v>
       </c>
       <c r="BA5" t="n">
-        <v>-22654000</v>
+        <v>-27251000</v>
       </c>
       <c r="BB5" t="n">
-        <v>60651000</v>
+        <v>52611000</v>
       </c>
       <c r="BC5" t="n">
-        <v>2416000</v>
+        <v>2421000</v>
       </c>
       <c r="BD5" t="n">
-        <v>4227000</v>
+        <v>5641000</v>
       </c>
       <c r="BE5" t="n">
-        <v>25408000</v>
+        <v>19366000</v>
       </c>
       <c r="BF5" t="n">
-        <v>2780000</v>
+        <v>10511000</v>
       </c>
       <c r="BG5" t="n">
-        <v>25820000</v>
+        <v>14672000</v>
       </c>
       <c r="BH5" t="n">
         <v>0</v>
       </c>
       <c r="BI5" t="n">
-        <v>44216000</v>
+        <v>35249000</v>
       </c>
       <c r="BJ5" t="n">
-        <v>7716000</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>1004000</v>
-      </c>
+        <v>2689000</v>
+      </c>
+      <c r="BK5" t="inlineStr"/>
       <c r="BL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>169000</v>
-      </c>
+        <v>281000</v>
+      </c>
+      <c r="BM5" t="inlineStr"/>
       <c r="BN5" t="n">
-        <v>776000</v>
+        <v>646000</v>
       </c>
       <c r="BO5" t="n">
-        <v>23189000</v>
+        <v>15908000</v>
       </c>
       <c r="BP5" t="n">
-        <v>6357000</v>
+        <v>2572000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>16832000</v>
+        <v>13336000</v>
       </c>
       <c r="BR5" t="n">
-        <v>3252000</v>
+        <v>4923000</v>
       </c>
       <c r="BS5" t="n">
-        <v>221000</v>
+        <v>19000</v>
       </c>
       <c r="BT5" t="n">
-        <v>10859000</v>
+        <v>5398000</v>
       </c>
       <c r="BU5" t="n">
-        <v>-2813000</v>
+        <v>-500000</v>
       </c>
       <c r="BV5" t="n">
-        <v>13672000</v>
+        <v>5898000</v>
       </c>
       <c r="BW5" t="n">
-        <v>1455000</v>
-      </c>
-      <c r="BX5" t="inlineStr"/>
+        <v>5385000</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>994000</v>
+      </c>
       <c r="BY5" t="n">
-        <v>1455000</v>
-      </c>
-      <c r="BZ5" t="n">
-        <v>1446000</v>
-      </c>
+        <v>4391000</v>
+      </c>
+      <c r="BZ5" t="inlineStr"/>
       <c r="CA5" t="n">
-        <v>1455000</v>
+        <v>4391000</v>
       </c>
     </row>
   </sheetData>
@@ -2839,508 +2839,508 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>5197000</v>
+        <v>-196000</v>
       </c>
       <c r="C2" t="n">
-        <v>-3055000</v>
+        <v>-17852000</v>
       </c>
       <c r="D2" t="n">
-        <v>872000</v>
-      </c>
-      <c r="E2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1442000</v>
+      </c>
       <c r="F2" t="n">
-        <v>-10765000</v>
+        <v>-15004000</v>
       </c>
       <c r="G2" t="n">
-        <v>4391000</v>
+        <v>980000</v>
       </c>
       <c r="H2" t="n">
-        <v>1000</v>
+        <v>1962000</v>
       </c>
       <c r="I2" t="n">
-        <v>3209000</v>
+        <v>3061000</v>
       </c>
       <c r="J2" t="n">
-        <v>1181000</v>
+        <v>-4043000</v>
       </c>
       <c r="K2" t="n">
-        <v>-4353000</v>
+        <v>-20527000</v>
       </c>
       <c r="L2" t="n">
-        <v>1159000</v>
-      </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+        <v>-165000</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1442000</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1442000</v>
+      </c>
       <c r="O2" t="n">
-        <v>-2183000</v>
+        <v>-17852000</v>
       </c>
       <c r="P2" t="n">
-        <v>-2183000</v>
+        <v>-17852000</v>
       </c>
       <c r="Q2" t="n">
-        <v>-3055000</v>
+        <v>-17852000</v>
       </c>
       <c r="R2" t="n">
-        <v>872000</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>-10428000</v>
+        <v>1676000</v>
       </c>
       <c r="T2" t="n">
-        <v>-1000</v>
-      </c>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
+        <v>-3547000</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>8351000</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>8351000</v>
       </c>
       <c r="Z2" t="n">
-        <v>-7901000</v>
+        <v>-12778000</v>
       </c>
       <c r="AA2" t="n">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>-7901000</v>
+        <v>-12778000</v>
       </c>
       <c r="AC2" t="n">
-        <v>-2526000</v>
+        <v>9650000</v>
       </c>
       <c r="AD2" t="n">
-        <v>338000</v>
+        <v>11876000</v>
       </c>
       <c r="AE2" t="n">
-        <v>-2864000</v>
+        <v>-2226000</v>
       </c>
       <c r="AF2" t="n">
-        <v>15962000</v>
-      </c>
-      <c r="AG2" t="inlineStr"/>
+        <v>14808000</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>-473000</v>
+      </c>
       <c r="AH2" t="n">
-        <v>-6811000</v>
+        <v>-4724000</v>
       </c>
       <c r="AI2" t="n">
-        <v>5484000</v>
+        <v>2688000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-693000</v>
+        <v>4842000</v>
       </c>
       <c r="AK2" t="n">
-        <v>4087000</v>
+        <v>-2417000</v>
       </c>
       <c r="AL2" t="n">
-        <v>2575000</v>
+        <v>240000</v>
       </c>
       <c r="AM2" t="n">
-        <v>6192000</v>
-      </c>
-      <c r="AN2" t="inlineStr"/>
+        <v>6879000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>573000</v>
+      </c>
       <c r="AO2" t="n">
-        <v>17007000</v>
+        <v>16365000</v>
       </c>
       <c r="AP2" t="n">
-        <v>17007000</v>
+        <v>16365000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>195000</v>
+        <v>-582000</v>
       </c>
       <c r="AR2" t="n">
-        <v>-6105000</v>
+        <v>-7669000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-13758000</v>
+        <v>6834000</v>
       </c>
       <c r="C3" t="n">
-        <v>-44732000</v>
+        <v>-18977000</v>
       </c>
       <c r="D3" t="n">
-        <v>2340000</v>
-      </c>
-      <c r="E3" t="inlineStr"/>
+        <v>21638000</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
       <c r="F3" t="n">
-        <v>-7595000</v>
+        <v>-7725000</v>
       </c>
       <c r="G3" t="n">
-        <v>3209000</v>
+        <v>18106000</v>
       </c>
       <c r="H3" t="n">
-        <v>1000</v>
+        <v>472000</v>
       </c>
       <c r="I3" t="n">
-        <v>18106000</v>
+        <v>981000</v>
       </c>
       <c r="J3" t="n">
-        <v>-14898000</v>
+        <v>16653000</v>
       </c>
       <c r="K3" t="n">
-        <v>-46878000</v>
+        <v>5969000</v>
       </c>
       <c r="L3" t="n">
-        <v>-107000</v>
-      </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+        <v>1631000</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
       <c r="O3" t="n">
-        <v>-42392000</v>
+        <v>2661000</v>
       </c>
       <c r="P3" t="n">
-        <v>-42392000</v>
+        <v>2661000</v>
       </c>
       <c r="Q3" t="n">
-        <v>-44732000</v>
+        <v>-18977000</v>
       </c>
       <c r="R3" t="n">
-        <v>2340000</v>
+        <v>21638000</v>
       </c>
       <c r="S3" t="n">
-        <v>38143000</v>
-      </c>
-      <c r="T3" t="inlineStr"/>
+        <v>-3875000</v>
+      </c>
+      <c r="T3" t="n">
+        <v>-4461000</v>
+      </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
+        <v>416000</v>
+      </c>
+      <c r="W3" t="n">
+        <v>416000</v>
+      </c>
+      <c r="X3" t="n">
         <v>0</v>
       </c>
-      <c r="W3" t="n">
+      <c r="Y3" t="n">
         <v>0</v>
       </c>
-      <c r="X3" t="n">
-        <v>37538000</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>37538000</v>
-      </c>
       <c r="Z3" t="n">
-        <v>-1778000</v>
+        <v>-3548000</v>
       </c>
       <c r="AA3" t="n">
-        <v>4100000</v>
+        <v>1500000</v>
       </c>
       <c r="AB3" t="n">
-        <v>-5878000</v>
+        <v>-5048000</v>
       </c>
       <c r="AC3" t="n">
-        <v>2383000</v>
+        <v>3718000</v>
       </c>
       <c r="AD3" t="n">
-        <v>4100000</v>
+        <v>6395000</v>
       </c>
       <c r="AE3" t="n">
-        <v>-1717000</v>
+        <v>-2677000</v>
       </c>
       <c r="AF3" t="n">
-        <v>-6163000</v>
-      </c>
-      <c r="AG3" t="inlineStr"/>
+        <v>14559000</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0</v>
+      </c>
       <c r="AH3" t="n">
-        <v>-11921000</v>
+        <v>-6500000</v>
       </c>
       <c r="AI3" t="n">
-        <v>-5496000</v>
+        <v>7838000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-8369000</v>
+        <v>11793000</v>
       </c>
       <c r="AK3" t="n">
-        <v>3367000</v>
+        <v>-1238000</v>
       </c>
       <c r="AL3" t="n">
-        <v>537000</v>
+        <v>-1120000</v>
       </c>
       <c r="AM3" t="n">
-        <v>11534000</v>
+        <v>6034000</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>-437000</v>
       </c>
       <c r="AO3" t="n">
-        <v>16432000</v>
+        <v>14278000</v>
       </c>
       <c r="AP3" t="n">
-        <v>16432000</v>
+        <v>14278000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-6140000</v>
+        <v>2213000</v>
       </c>
       <c r="AR3" t="n">
-        <v>-3812000</v>
+        <v>-11952000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>6834000</v>
+        <v>-13758000</v>
       </c>
       <c r="C4" t="n">
-        <v>-18977000</v>
+        <v>-44732000</v>
       </c>
       <c r="D4" t="n">
-        <v>21638000</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
+        <v>2340000</v>
+      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>-7725000</v>
+        <v>-7595000</v>
       </c>
       <c r="G4" t="n">
+        <v>3209000</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I4" t="n">
         <v>18106000</v>
       </c>
-      <c r="H4" t="n">
-        <v>472000</v>
-      </c>
-      <c r="I4" t="n">
-        <v>981000</v>
-      </c>
       <c r="J4" t="n">
-        <v>16653000</v>
+        <v>-14898000</v>
       </c>
       <c r="K4" t="n">
-        <v>5969000</v>
+        <v>-46878000</v>
       </c>
       <c r="L4" t="n">
-        <v>1631000</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
+        <v>-107000</v>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
-        <v>2661000</v>
+        <v>-42392000</v>
       </c>
       <c r="P4" t="n">
-        <v>2661000</v>
+        <v>-42392000</v>
       </c>
       <c r="Q4" t="n">
-        <v>-18977000</v>
+        <v>-44732000</v>
       </c>
       <c r="R4" t="n">
-        <v>21638000</v>
+        <v>2340000</v>
       </c>
       <c r="S4" t="n">
-        <v>-3875000</v>
-      </c>
-      <c r="T4" t="n">
-        <v>-4461000</v>
-      </c>
+        <v>38143000</v>
+      </c>
+      <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>416000</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>416000</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
+        <v>37538000</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>37538000</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>-1778000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>4100000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>-5878000</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>2383000</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>4100000</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>-1717000</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>-6163000</v>
+      </c>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="n">
+        <v>-11921000</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>-5496000</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>-8369000</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>3367000</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>537000</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>11534000</v>
+      </c>
+      <c r="AN4" t="n">
         <v>0</v>
       </c>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>-3548000</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1500000</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>-5048000</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>3718000</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>6395000</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>-2677000</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>14559000</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>-6500000</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>7838000</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>11793000</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>-1238000</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>-1120000</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>6034000</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>-437000</v>
-      </c>
       <c r="AO4" t="n">
-        <v>14278000</v>
+        <v>16432000</v>
       </c>
       <c r="AP4" t="n">
-        <v>14278000</v>
+        <v>16432000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>2213000</v>
+        <v>-6140000</v>
       </c>
       <c r="AR4" t="n">
-        <v>-11952000</v>
+        <v>-3812000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-196000</v>
+        <v>5197000</v>
       </c>
       <c r="C5" t="n">
-        <v>-17852000</v>
+        <v>-3055000</v>
       </c>
       <c r="D5" t="n">
+        <v>872000</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="n">
+        <v>-10765000</v>
+      </c>
+      <c r="G5" t="n">
+        <v>4391000</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3209000</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1181000</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-4353000</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1159000</v>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="n">
+        <v>-2183000</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-2183000</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-3055000</v>
+      </c>
+      <c r="R5" t="n">
+        <v>872000</v>
+      </c>
+      <c r="S5" t="n">
+        <v>-10428000</v>
+      </c>
+      <c r="T5" t="n">
+        <v>-1000</v>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="n">
         <v>0</v>
       </c>
-      <c r="E5" t="n">
-        <v>1442000</v>
-      </c>
-      <c r="F5" t="n">
-        <v>-15004000</v>
-      </c>
-      <c r="G5" t="n">
-        <v>980000</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1962000</v>
-      </c>
-      <c r="I5" t="n">
-        <v>3061000</v>
-      </c>
-      <c r="J5" t="n">
-        <v>-4043000</v>
-      </c>
-      <c r="K5" t="n">
-        <v>-20527000</v>
-      </c>
-      <c r="L5" t="n">
-        <v>-165000</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1442000</v>
-      </c>
-      <c r="N5" t="n">
-        <v>1442000</v>
-      </c>
-      <c r="O5" t="n">
-        <v>-17852000</v>
-      </c>
-      <c r="P5" t="n">
-        <v>-17852000</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>-17852000</v>
-      </c>
-      <c r="R5" t="n">
+      <c r="Y5" t="n">
         <v>0</v>
       </c>
-      <c r="S5" t="n">
-        <v>1676000</v>
-      </c>
-      <c r="T5" t="n">
-        <v>-3547000</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>8351000</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>8351000</v>
-      </c>
       <c r="Z5" t="n">
-        <v>-12778000</v>
+        <v>-7901000</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>-12778000</v>
+        <v>-7901000</v>
       </c>
       <c r="AC5" t="n">
-        <v>9650000</v>
+        <v>-2526000</v>
       </c>
       <c r="AD5" t="n">
-        <v>11876000</v>
+        <v>338000</v>
       </c>
       <c r="AE5" t="n">
-        <v>-2226000</v>
+        <v>-2864000</v>
       </c>
       <c r="AF5" t="n">
-        <v>14808000</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>-473000</v>
-      </c>
+        <v>15962000</v>
+      </c>
+      <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="n">
-        <v>-4724000</v>
+        <v>-6811000</v>
       </c>
       <c r="AI5" t="n">
-        <v>2688000</v>
+        <v>5484000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>4842000</v>
+        <v>-693000</v>
       </c>
       <c r="AK5" t="n">
-        <v>-2417000</v>
+        <v>4087000</v>
       </c>
       <c r="AL5" t="n">
-        <v>240000</v>
+        <v>2575000</v>
       </c>
       <c r="AM5" t="n">
-        <v>6879000</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>573000</v>
-      </c>
+        <v>6192000</v>
+      </c>
+      <c r="AN5" t="inlineStr"/>
       <c r="AO5" t="n">
-        <v>16365000</v>
+        <v>17007000</v>
       </c>
       <c r="AP5" t="n">
-        <v>16365000</v>
+        <v>17007000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-582000</v>
+        <v>195000</v>
       </c>
       <c r="AR5" t="n">
-        <v>-7669000</v>
+        <v>-6105000</v>
       </c>
     </row>
   </sheetData>
@@ -3830,197 +3830,197 @@
       </c>
       <c r="CQ1" t="inlineStr">
         <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="CR1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="CS1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="CT1" t="inlineStr">
+        <is>
           <t>shortName</t>
         </is>
       </c>
-      <c r="CR1" t="inlineStr">
+      <c r="CU1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="CV1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="CW1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="CX1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="CY1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="CZ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>earningsCallTimestampStart</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>earningsCallTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>priceToBook</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
         <is>
           <t>corporateActions</t>
         </is>
       </c>
-      <c r="CS1" t="inlineStr">
+      <c r="DQ1" t="inlineStr">
         <is>
           <t>regularMarketTime</t>
         </is>
       </c>
-      <c r="CT1" t="inlineStr">
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
         <is>
           <t>exchange</t>
         </is>
       </c>
-      <c r="CU1" t="inlineStr">
+      <c r="DV1" t="inlineStr">
         <is>
           <t>messageBoardId</t>
         </is>
       </c>
-      <c r="CV1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
         <is>
           <t>exchangeTimezoneName</t>
         </is>
       </c>
-      <c r="CW1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
         <is>
           <t>exchangeTimezoneShortName</t>
         </is>
       </c>
-      <c r="CX1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>gmtOffSetMilliseconds</t>
         </is>
       </c>
-      <c r="CY1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="CZ1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>esgPopulated</t>
         </is>
       </c>
-      <c r="DA1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>hasPrePostMarketData</t>
         </is>
       </c>
-      <c r="DB1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DC1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DD1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DE1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DF1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>earningsCallTimestampStart</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>earningsCallTimestampEnd</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>priceToBook</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
         </is>
       </c>
       <c r="ED1" t="inlineStr">
@@ -4123,64 +4123,64 @@
         <v>4</v>
       </c>
       <c r="U2" t="n">
-        <v>1.695</v>
+        <v>1.565</v>
       </c>
       <c r="V2" t="n">
         <v>2</v>
       </c>
       <c r="W2" t="n">
-        <v>2</v>
+        <v>1.59</v>
       </c>
       <c r="X2" t="n">
-        <v>2</v>
+        <v>1.77</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.695</v>
+        <v>1.565</v>
       </c>
       <c r="Z2" t="n">
         <v>2</v>
       </c>
       <c r="AA2" t="n">
-        <v>2</v>
+        <v>1.59</v>
       </c>
       <c r="AB2" t="n">
-        <v>2</v>
+        <v>1.77</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.665</v>
+        <v>0.666</v>
       </c>
       <c r="AE2" t="n">
-        <v>3</v>
+        <v>558</v>
       </c>
       <c r="AF2" t="n">
-        <v>3</v>
+        <v>558</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AL2" t="n">
-        <v>7672021</v>
+        <v>7083606</v>
       </c>
       <c r="AM2" t="n">
-        <v>7739914</v>
+        <v>7377813</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.77</v>
+        <v>1.585</v>
       </c>
       <c r="AO2" t="n">
         <v>3.1</v>
@@ -4189,16 +4189,16 @@
         <v>3.1</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.7</v>
+        <v>1.585</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.06352693600000001</v>
+        <v>0.05865466</v>
       </c>
       <c r="AS2" t="n">
-        <v>2.07</v>
+        <v>2.0409</v>
       </c>
       <c r="AT2" t="n">
-        <v>2.2244</v>
+        <v>2.224125</v>
       </c>
       <c r="AU2" t="n">
         <v>0</v>
@@ -4215,7 +4215,7 @@
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>74874760</v>
+        <v>74761608</v>
       </c>
       <c r="AZ2" t="n">
         <v>-0.04537</v>
@@ -4254,16 +4254,16 @@
         <v>-1.21</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.62</v>
+        <v>0.619</v>
       </c>
       <c r="BM2" t="n">
-        <v>7.681</v>
+        <v>7.669</v>
       </c>
       <c r="BN2" t="n">
-        <v>0.05076146</v>
+        <v>-0.19543147</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.27449715</v>
+        <v>0.24487448</v>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="BQ2" t="n">
-        <v>1.695</v>
+        <v>1.565</v>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
@@ -4364,144 +4364,144 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="CQ2" t="inlineStr">
+      <c r="CQ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR2" t="inlineStr">
+        <is>
+          <t>1.59 - 1.77</t>
+        </is>
+      </c>
+      <c r="CS2" t="inlineStr">
+        <is>
+          <t>Milan</t>
+        </is>
+      </c>
+      <c r="CT2" t="inlineStr">
         <is>
           <t>PARAGON</t>
         </is>
       </c>
-      <c r="CR2" t="inlineStr">
+      <c r="CU2" t="n">
+        <v>9</v>
+      </c>
+      <c r="CV2" t="n">
+        <v>-0.01999998</v>
+      </c>
+      <c r="CW2" t="n">
+        <v>-0.012618284</v>
+      </c>
+      <c r="CX2" t="inlineStr">
+        <is>
+          <t>1.585 - 3.1</t>
+        </is>
+      </c>
+      <c r="CY2" t="n">
+        <v>-1.5349998</v>
+      </c>
+      <c r="CZ2" t="n">
+        <v>-0.49516127</v>
+      </c>
+      <c r="DA2" t="n">
+        <v>-19.543148</v>
+      </c>
+      <c r="DB2" t="n">
+        <v>1755581400</v>
+      </c>
+      <c r="DC2" t="n">
+        <v>1755581400</v>
+      </c>
+      <c r="DD2" t="n">
+        <v>1763031540</v>
+      </c>
+      <c r="DE2" t="n">
+        <v>1763031540</v>
+      </c>
+      <c r="DF2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DG2" t="n">
+        <v>-1.21</v>
+      </c>
+      <c r="DH2" t="n">
+        <v>-0.47589993</v>
+      </c>
+      <c r="DI2" t="n">
+        <v>-0.2331814</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>-0.65912485</v>
+      </c>
+      <c r="DK2" t="n">
+        <v>-0.29635245</v>
+      </c>
+      <c r="DL2" t="n">
+        <v>-0.72756857</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>20</v>
+      </c>
+      <c r="DN2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DP2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="CS2" t="n">
-        <v>1769785834</v>
-      </c>
-      <c r="CT2" t="inlineStr">
+      <c r="DQ2" t="n">
+        <v>1781709880</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>1.565</v>
+      </c>
+      <c r="DT2" t="inlineStr">
+        <is>
+          <t>PREPRE</t>
+        </is>
+      </c>
+      <c r="DU2" t="inlineStr">
         <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="CU2" t="inlineStr">
+      <c r="DV2" t="inlineStr">
         <is>
           <t>finmb_693327</t>
         </is>
       </c>
-      <c r="CV2" t="inlineStr">
+      <c r="DW2" t="inlineStr">
         <is>
           <t>Europe/Rome</t>
         </is>
       </c>
-      <c r="CW2" t="inlineStr">
+      <c r="DX2" t="inlineStr">
         <is>
           <t>CEST</t>
         </is>
       </c>
-      <c r="CX2" t="n">
+      <c r="DY2" t="n">
         <v>7200000</v>
       </c>
-      <c r="CY2" t="inlineStr">
+      <c r="DZ2" t="inlineStr">
         <is>
           <t>it_market</t>
         </is>
       </c>
-      <c r="CZ2" t="b">
+      <c r="EA2" t="b">
         <v>0</v>
       </c>
-      <c r="DA2" t="b">
+      <c r="EB2" t="b">
         <v>0</v>
       </c>
-      <c r="DB2" t="n">
+      <c r="EC2" t="n">
         <v>1707292800000</v>
-      </c>
-      <c r="DC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DD2" t="inlineStr">
-        <is>
-          <t>2.0 - 2.0</t>
-        </is>
-      </c>
-      <c r="DE2" t="inlineStr">
-        <is>
-          <t>Milan</t>
-        </is>
-      </c>
-      <c r="DF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DG2" t="n">
-        <v>-0.07499993000000001</v>
-      </c>
-      <c r="DH2" t="n">
-        <v>-0.04237284</v>
-      </c>
-      <c r="DI2" t="inlineStr">
-        <is>
-          <t>1.77 - 3.1</t>
-        </is>
-      </c>
-      <c r="DJ2" t="n">
-        <v>-1.4049999</v>
-      </c>
-      <c r="DK2" t="n">
-        <v>-0.45322576</v>
-      </c>
-      <c r="DL2" t="n">
-        <v>5.076146</v>
-      </c>
-      <c r="DM2" t="n">
-        <v>1755581400</v>
-      </c>
-      <c r="DN2" t="n">
-        <v>1755581400</v>
-      </c>
-      <c r="DO2" t="n">
-        <v>1763031540</v>
-      </c>
-      <c r="DP2" t="n">
-        <v>1763031540</v>
-      </c>
-      <c r="DQ2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DR2" t="n">
-        <v>-1.21</v>
-      </c>
-      <c r="DS2" t="inlineStr">
-        <is>
-          <t>PRE</t>
-        </is>
-      </c>
-      <c r="DT2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DU2" t="n">
-        <v>1.695</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>-0.37499988</v>
-      </c>
-      <c r="DW2" t="n">
-        <v>-0.18115936</v>
-      </c>
-      <c r="DX2" t="n">
-        <v>-0.5294</v>
-      </c>
-      <c r="DY2" t="n">
-        <v>-0.23799676</v>
-      </c>
-      <c r="DZ2" t="n">
-        <v>-0.7880056</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>20</v>
-      </c>
-      <c r="EB2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EC2" t="b">
-        <v>0</v>
       </c>
       <c r="ED2" t="inlineStr"/>
     </row>
